--- a/data/sars/pacific/tables/Pacific_1999_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_1999_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD15B88-7F03-044F-AC1E-42D484A2431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6F37FA-FE9E-F844-91C3-44A775511AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{C55E6382-48A9-034D-B9B7-E55AB40E4896}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="35">
   <si>
     <t>species</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>Eastern North Pacific Southern Resident</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -980,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B1DD0-7EB5-9B4E-86CE-839F3C5B4565}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -995,7 +1001,7 @@
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1029,8 +1035,11 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="K2" t="s">
         <v>16</v>
       </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1099,8 +1111,11 @@
       <c r="K3" t="s">
         <v>17</v>
       </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1134,8 +1149,11 @@
       <c r="K4" t="s">
         <v>17</v>
       </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1169,8 +1187,11 @@
       <c r="K5" t="s">
         <v>17</v>
       </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1225,11 @@
       <c r="K6" t="s">
         <v>17</v>
       </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1239,8 +1263,11 @@
       <c r="K7" t="s">
         <v>17</v>
       </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1274,8 +1301,11 @@
       <c r="K8" t="s">
         <v>17</v>
       </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1309,8 +1339,11 @@
       <c r="K9" t="s">
         <v>17</v>
       </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1344,8 +1377,11 @@
       <c r="K10" t="s">
         <v>16</v>
       </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1415,11 @@
       <c r="K11" t="s">
         <v>16</v>
       </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1413,6 +1452,9 @@
       </c>
       <c r="K12" t="s">
         <v>16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
